--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.32482771731451</v>
+        <v>2.652784504063608</v>
       </c>
       <c r="D2" t="n">
-        <v>39.19292490639209</v>
+        <v>6.368850297288716</v>
       </c>
       <c r="E2" t="n">
-        <v>11.28126980960231</v>
+        <v>1.833206344060375</v>
       </c>
       <c r="F2" t="n">
-        <v>14.15632456307176</v>
+        <v>2.30040274149916</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.50861812854691</v>
+        <v>2.357650445888873</v>
       </c>
       <c r="D3" t="n">
-        <v>29.62127786234061</v>
+        <v>4.813457652630349</v>
       </c>
       <c r="E3" t="n">
-        <v>11.28126980960231</v>
+        <v>1.833206344060375</v>
       </c>
       <c r="F3" t="n">
-        <v>14.15632456307176</v>
+        <v>2.30040274149916</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.7619465964028</v>
+        <v>6.298816321915456</v>
       </c>
       <c r="D4" t="n">
-        <v>38.72529177362711</v>
+        <v>6.292859913214406</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28126980960231</v>
+        <v>1.833206344060375</v>
       </c>
       <c r="F4" t="n">
-        <v>14.15632456307176</v>
+        <v>2.30040274149916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.46972273109911</v>
+        <v>3.651329943803605</v>
       </c>
       <c r="D5" t="n">
-        <v>12.5099960031968</v>
+        <v>2.032874350519481</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28126980960231</v>
+        <v>1.833206344060375</v>
       </c>
       <c r="F5" t="n">
-        <v>14.15632456307176</v>
+        <v>2.30040274149916</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.112864309558022</v>
+        <v>0.1808404503031786</v>
       </c>
       <c r="D6" t="n">
-        <v>1.204155341956384</v>
+        <v>0.1956752430679123</v>
       </c>
       <c r="E6" t="n">
-        <v>11.28126980960231</v>
+        <v>1.833206344060375</v>
       </c>
       <c r="F6" t="n">
-        <v>14.15632456307176</v>
+        <v>2.30040274149916</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.47664612340359</v>
+        <v>2.352454995053084</v>
       </c>
       <c r="D7" t="n">
-        <v>14.96882413229605</v>
+        <v>2.432433921498108</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28126980960231</v>
+        <v>1.833206344060375</v>
       </c>
       <c r="F7" t="n">
-        <v>14.15632456307176</v>
+        <v>2.30040274149916</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
